--- a/gamedata/Stage.xlsx
+++ b/gamedata/Stage.xlsx
@@ -611,30 +611,30 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" s="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>試營運</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>101,102,101,102,103</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>501,502,503</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>302</t>
         </is>
@@ -642,6 +642,44 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" s="5">
       <c r="A6" s="3" t="n"/>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>大排長龍</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>115,112,113,125,118,111,120,122,133,123</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,127,128,129,130,131,132,133,134,136,137,101,102,103,113,117,129,111</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>103,117,114</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>511,512,513,514,515,516,517,518,501,502,503,511,512,513,514,515,516,517,518,501,502,503,511,512,513,514,515,516,517,518,501,502,503,511,512,513</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="5">
       <c r="A7" s="3" t="n"/>
